--- a/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,82</t>
+          <t>0,0; 17,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,03</t>
+          <t>1,7; 16,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,83</t>
+          <t>1,15; 10,27</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,9</t>
+          <t>0,0; 18,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,55</t>
+          <t>0,0; 9,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 10,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 14,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,49</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,42</t>
+          <t>1,13; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,59</t>
+          <t>0,47; 3,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,69</t>
+          <t>0,51; 2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,65</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5022</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>533; 5300</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3297</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3172</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4502</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4466</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>718; 6387</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3099</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3397</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3157</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4296</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3166</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3258</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3125</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3938</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5603</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3475</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3085</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4655</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2477</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5416</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4994</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1836; 8510</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>673; 5186</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>605; 5577</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1371; 8042</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>628; 6243</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2576; 10070</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,3</t>
+          <t>0,0; 17,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,94</t>
+          <t>1,69; 16,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,26</t>
+          <t>0,0; 12,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,27</t>
+          <t>1,16; 9,88</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,0</t>
+          <t>0,0; 16,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,74</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
     </row>
@@ -1018,37 +1018,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,87</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,21</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,67</t>
+          <t>0,0; 9,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 11,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,24</t>
+          <t>0,92; 4,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,6</t>
+          <t>0,47; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,31; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,99</t>
+          <t>0,51; 3,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,83; 3,4</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5022</t>
+          <t>0; 5077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3209</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>533; 5300</t>
+          <t>530; 5094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,27 +1437,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3297</t>
+          <t>0; 3290</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3172</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>0; 4787</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4466</t>
+          <t>0; 4489</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>718; 6387</t>
+          <t>720; 6148</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3099</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 3156</t>
         </is>
       </c>
     </row>
@@ -1753,17 +1753,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 2558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 4010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 4633</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3258</t>
+          <t>0; 3104</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 2759</t>
         </is>
       </c>
     </row>
@@ -1916,37 +1916,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3938</t>
+          <t>0; 3795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5603</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3475</t>
+          <t>0; 3109</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>0; 3039</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4655</t>
+          <t>0; 4188</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2477</t>
+          <t>0; 3437</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5416</t>
+          <t>0; 4566</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1836; 8510</t>
+          <t>1497; 8050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>673; 5186</t>
+          <t>672; 6954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>605; 5577</t>
+          <t>602; 5531</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1371; 8042</t>
+          <t>1373; 8220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>628; 6243</t>
+          <t>629; 5706</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2576; 10070</t>
+          <t>2575; 10557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,95%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,5%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,28</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,37</t>
+          <t>1,7; 16,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,88</t>
+          <t>1,1; 10,83</t>
         </is>
       </c>
     </row>
@@ -745,22 +745,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,42</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,47</t>
+          <t>0,0; 13,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,24</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,47; 4,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,95</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,83</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,89</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,9; 5,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,05</t>
+          <t>0,51; 2,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,16; 1,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,4</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2034</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5077</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3447</t>
+          <t>0; 3254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>530; 5094</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 3502</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>532; 5016</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4787</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4489</t>
+          <t>0; 4441</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>720; 6148</t>
+          <t>687; 6734</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3085</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3156</t>
+          <t>0; 3046</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>813</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2558</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4010</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3667</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4633</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3104</t>
+          <t>0; 3426</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2759</t>
+          <t>0; 3085</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4666</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2668</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>0; 3648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3109</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3039</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4188</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3437</t>
+          <t>0; 3420</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 5114</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4028</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>670; 6599</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>608; 5694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1497; 8050</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>672; 6954</t>
+          <t>0; 5206</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>602; 5531</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>1461; 8802</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1373; 8220</t>
+          <t>1366; 7249</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>629; 5706</t>
+          <t>624; 6247</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2575; 10557</t>
+          <t>2439; 9734</t>
         </is>
       </c>
     </row>
